--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30640,6 +30640,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1317" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30663,6 +30663,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1318" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1319" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30709,6 +30709,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1320" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30717,7 +30717,7 @@
         <v>3000</v>
       </c>
       <c r="C1320" t="n">
-        <v>3.05999994277954</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="D1320" t="n">
         <v>3.01999998092651</v>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30573,19 +30573,19 @@
     </row>
     <row r="1314">
       <c r="A1314" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1314" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C1314" t="n">
         <v>3.07999992370605</v>
       </c>
       <c r="D1314" t="n">
-        <v>3.07999992370605</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="E1314" t="n">
-        <v>3.07999992370605</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="F1314" t="n">
         <v>3.07999992370605</v>
@@ -30596,7 +30596,7 @@
     </row>
     <row r="1315">
       <c r="A1315" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1315" t="n">
         <v>0</v>
@@ -30619,7 +30619,7 @@
     </row>
     <row r="1316">
       <c r="A1316" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1316" t="n">
         <v>0</v>
@@ -30642,7 +30642,7 @@
     </row>
     <row r="1317">
       <c r="A1317" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1317" t="n">
         <v>0</v>
@@ -30665,7 +30665,7 @@
     </row>
     <row r="1318">
       <c r="A1318" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1318" t="n">
         <v>0</v>
@@ -30688,22 +30688,22 @@
     </row>
     <row r="1319">
       <c r="A1319" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1319" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="C1319" t="n">
-        <v>3.11999988555908</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="D1319" t="n">
-        <v>3.11999988555908</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="E1319" t="n">
-        <v>3.11999988555908</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="F1319" t="n">
-        <v>3.11999988555908</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="G1319" t="s">
         <v>7</v>
@@ -30711,7 +30711,7 @@
     </row>
     <row r="1320">
       <c r="A1320" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1320" t="n">
         <v>3000</v>
@@ -30720,15 +30720,38 @@
         <v>3.11999988555908</v>
       </c>
       <c r="D1320" t="n">
-        <v>3.01999998092651</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="E1320" t="n">
-        <v>3.01999998092651</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="F1320" t="n">
         <v>3.11999988555908</v>
       </c>
       <c r="G1320" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1321" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152057647705</v>
+        <v>3.06152081489563</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502306938171</v>
+        <v>2.68502330780029</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278810501099</v>
+        <v>3.46278786659241</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453947067261</v>
+        <v>3.27453923225403</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426263809204</v>
+        <v>3.30426287651062</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306469917297</v>
+        <v>3.43306446075439</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555309295654</v>
+        <v>3.16555285453796</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.6312210559845</v>
+        <v>3.63122129440308</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002335548401</v>
+        <v>3.76002311706543</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571424484253</v>
+        <v>3.68571448326111</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.64112901687622</v>
+        <v>3.6411292552948</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520738601685</v>
+        <v>2.66520762443542</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700446128845</v>
+        <v>3.54700469970703</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -34796,6 +34796,32 @@
         <v>3.16000008583069</v>
       </c>
       <c r="H1324" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="H1325" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152081489563</v>
+        <v>3.06152057647705</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502330780029</v>
+        <v>2.68502306938171</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278786659241</v>
+        <v>3.46278810501099</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453923225403</v>
+        <v>3.27453947067261</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426287651062</v>
+        <v>3.30426263809204</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306446075439</v>
+        <v>3.43306469917297</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555285453796</v>
+        <v>3.16555309295654</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.63122129440308</v>
+        <v>3.6312210559845</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002311706543</v>
+        <v>3.76002335548401</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571448326111</v>
+        <v>3.68571424484253</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.6411292552948</v>
+        <v>3.64112901687622</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520762443542</v>
+        <v>2.66520738601685</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700469970703</v>
+        <v>3.54700446128845</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -34822,6 +34822,32 @@
         <v>3.09999990463257</v>
       </c>
       <c r="H1325" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1326" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1326" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30870,6 +30870,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1327" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30893,6 +30893,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1328">
+      <c r="A1328" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1328" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -30916,6 +30916,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1329">
+      <c r="A1329" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1329" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -31047,8 +31047,31 @@
       <c r="E1334" t="n">
         <v>3.14000010490417</v>
       </c>
-      <c r="F1334"/>
+      <c r="F1334" t="n">
+        <v>3.1800000667572</v>
+      </c>
       <c r="G1334" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1335" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F1335"/>
+      <c r="G1335" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -31070,7 +31070,9 @@
       <c r="E1335" t="n">
         <v>3.14000010490417</v>
       </c>
-      <c r="F1335"/>
+      <c r="F1335" t="n">
+        <v>3.07999992370605</v>
+      </c>
       <c r="G1335" t="s">
         <v>7</v>
       </c>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -31077,6 +31077,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1336" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -31100,6 +31100,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1337">
+      <c r="A1337" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1337" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1337" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -31146,6 +31146,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1339">
+      <c r="A1339" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1339" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C1339" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="D1339" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1339" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G1339" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152081489563</v>
+        <v>3.06152057647705</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502330780029</v>
+        <v>2.68502306938171</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278786659241</v>
+        <v>3.46278810501099</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453923225403</v>
+        <v>3.27453947067261</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426287651062</v>
+        <v>3.30426263809204</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306446075439</v>
+        <v>3.43306469917297</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555285453796</v>
+        <v>3.16555309295654</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.63122129440308</v>
+        <v>3.6312210559845</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002311706543</v>
+        <v>3.76002335548401</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571448326111</v>
+        <v>3.68571424484253</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.6411292552948</v>
+        <v>3.64112901687622</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520762443542</v>
+        <v>2.66520738601685</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700469970703</v>
+        <v>3.54700446128845</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -35238,6 +35238,32 @@
         <v>3.22000002861023</v>
       </c>
       <c r="H1341" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1342" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1342" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="D1342" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1342" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152057647705</v>
+        <v>3.06152081489563</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502306938171</v>
+        <v>2.68502330780029</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278810501099</v>
+        <v>3.46278786659241</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453947067261</v>
+        <v>3.27453923225403</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426263809204</v>
+        <v>3.30426287651062</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306469917297</v>
+        <v>3.43306446075439</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555309295654</v>
+        <v>3.16555285453796</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.6312210559845</v>
+        <v>3.63122129440308</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002335548401</v>
+        <v>3.76002311706543</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571424484253</v>
+        <v>3.68571448326111</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.64112901687622</v>
+        <v>3.6411292552948</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520738601685</v>
+        <v>2.66520762443542</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700446128845</v>
+        <v>3.54700469970703</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -39322,6 +39322,64 @@
         <v>0</v>
       </c>
       <c r="I1343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1344" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1344" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1344" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E1344" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1344" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1345" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1345" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D1345" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E1345" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="H1345" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1345" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152081489563</v>
+        <v>3.06152057647705</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502330780029</v>
+        <v>2.68502306938171</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278786659241</v>
+        <v>3.46278810501099</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453923225403</v>
+        <v>3.27453947067261</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426287651062</v>
+        <v>3.30426263809204</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306446075439</v>
+        <v>3.43306469917297</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555285453796</v>
+        <v>3.16555309295654</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.63122129440308</v>
+        <v>3.6312210559845</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002311706543</v>
+        <v>3.76002335548401</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571448326111</v>
+        <v>3.68571424484253</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.6411292552948</v>
+        <v>3.64112901687622</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520762443542</v>
+        <v>2.66520738601685</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700469970703</v>
+        <v>3.54700446128845</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -39380,6 +39380,35 @@
         <v>14000</v>
       </c>
       <c r="I1345" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1346" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1346" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D1346" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1346" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="H1346" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1346" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152057647705</v>
+        <v>3.06152081489563</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502306938171</v>
+        <v>2.68502330780029</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278810501099</v>
+        <v>3.46278786659241</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453947067261</v>
+        <v>3.27453923225403</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426263809204</v>
+        <v>3.30426287651062</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306469917297</v>
+        <v>3.43306446075439</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555309295654</v>
+        <v>3.16555285453796</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.6312210559845</v>
+        <v>3.63122129440308</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002335548401</v>
+        <v>3.76002311706543</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571424484253</v>
+        <v>3.68571448326111</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.64112901687622</v>
+        <v>3.6411292552948</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520738601685</v>
+        <v>2.66520762443542</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700446128845</v>
+        <v>3.54700469970703</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -39409,6 +39409,35 @@
         <v>10000</v>
       </c>
       <c r="I1346" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1347" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1347" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1347" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1347" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I1347" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -39441,6 +39441,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1348" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1348" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D1348" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="H1348" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I1348" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -39470,6 +39470,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1349">
+      <c r="A1349" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1349" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1349" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D1349" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H1349" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I1349" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152081489563</v>
+        <v>3.06152057647705</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502330780029</v>
+        <v>2.68502306938171</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278786659241</v>
+        <v>3.46278810501099</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453923225403</v>
+        <v>3.27453947067261</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426287651062</v>
+        <v>3.30426263809204</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306446075439</v>
+        <v>3.43306469917297</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555285453796</v>
+        <v>3.16555309295654</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.63122129440308</v>
+        <v>3.6312210559845</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002311706543</v>
+        <v>3.76002335548401</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571448326111</v>
+        <v>3.68571424484253</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.6411292552948</v>
+        <v>3.64112901687622</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520762443542</v>
+        <v>2.66520738601685</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700469970703</v>
+        <v>3.54700446128845</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -39499,6 +39499,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1350">
+      <c r="A1350" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1350" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1350" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1350" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1350" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152057647705</v>
+        <v>3.06152081489563</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502306938171</v>
+        <v>2.68502330780029</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7940092086792</v>
+        <v>2.79400944709778</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8534562587738</v>
+        <v>2.85345649719238</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278810501099</v>
+        <v>3.46278786659241</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297218322754</v>
+        <v>3.44297242164612</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453947067261</v>
+        <v>3.27453923225403</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426263809204</v>
+        <v>3.30426287651062</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306469917297</v>
+        <v>3.43306446075439</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.3538019657135</v>
+        <v>3.35380172729492</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555309295654</v>
+        <v>3.16555285453796</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361764907837</v>
+        <v>3.37361741065979</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.6312210559845</v>
+        <v>3.63122129440308</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002335548401</v>
+        <v>3.76002311706543</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571424484253</v>
+        <v>3.68571448326111</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635971069336</v>
+        <v>3.61635947227478</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.64112901687622</v>
+        <v>3.6411292552948</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645174980164</v>
+        <v>3.60645198822021</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186652183533</v>
+        <v>3.56186628341675</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225808143616</v>
+        <v>2.98225831985474</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520738601685</v>
+        <v>2.66520762443542</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838719367981</v>
+        <v>3.39838743209839</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700446128845</v>
+        <v>3.54700469970703</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940081596375</v>
+        <v>3.28940105438232</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11106014251709</v>
+        <v>3.11105990409851</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087582588196</v>
+        <v>3.13087558746338</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327194213867</v>
+        <v>2.87327218055725</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253443717957</v>
+        <v>2.95253467559814</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.14078378677368</v>
+        <v>3.1407835483551</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801832199097</v>
+        <v>3.43801856040955</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847923278809</v>
+        <v>3.38847947120667</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986196517944</v>
+        <v>3.23986172676086</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.22004628181458</v>
+        <v>3.220046043396</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023036003113</v>
+        <v>3.20023059844971</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050695419312</v>
+        <v>3.17050719261169</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912446022034</v>
+        <v>3.31912422180176</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875582695007</v>
+        <v>3.35875606536865</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737333297729</v>
+        <v>3.50737309455872</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728129386902</v>
+        <v>3.51728105545044</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663582801819</v>
+        <v>3.58663606643677</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718901634216</v>
+        <v>3.52718877792358</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.4281108379364</v>
+        <v>3.42811059951782</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829515457153</v>
+        <v>3.40829491615295</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903242111206</v>
+        <v>3.32903218269348</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976944923401</v>
+        <v>3.24976968765259</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -39525,6 +39525,64 @@
         <v>0</v>
       </c>
       <c r="I1350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1351" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1351" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1351" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1351" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1352" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1352" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1352" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1352" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IDNTT.MI.xlsx
+++ b/data/IDNTT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.06152081489563</v>
+        <v>3.06152057647705</v>
       </c>
       <c r="H5" t="n">
         <v>648000</v>
@@ -630,7 +630,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68502330780029</v>
+        <v>2.68502306938171</v>
       </c>
       <c r="H9" t="n">
         <v>117000</v>
@@ -746,7 +746,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G13" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H13" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H15" t="n">
         <v>19000</v>
@@ -949,7 +949,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G20" t="n">
-        <v>2.79400944709778</v>
+        <v>2.7940092086792</v>
       </c>
       <c r="H20" t="n">
         <v>40000</v>
@@ -1268,7 +1268,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>2.85345649719238</v>
+        <v>2.8534562587738</v>
       </c>
       <c r="H31" t="n">
         <v>14000</v>
@@ -1355,7 +1355,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G34" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H34" t="n">
         <v>681000</v>
@@ -1442,7 +1442,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H37" t="n">
         <v>35000</v>
@@ -1529,7 +1529,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H40" t="n">
         <v>21000</v>
@@ -1587,7 +1587,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G42" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H42" t="n">
         <v>78000</v>
@@ -1616,7 +1616,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G43" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H43" t="n">
         <v>64000</v>
@@ -1674,7 +1674,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G45" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H45" t="n">
         <v>20000</v>
@@ -1703,7 +1703,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G46" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H46" t="n">
         <v>24000</v>
@@ -1761,7 +1761,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G48" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H48" t="n">
         <v>21000</v>
@@ -1790,7 +1790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G49" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H49" t="n">
         <v>6000</v>
@@ -1848,7 +1848,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G51" t="n">
-        <v>3.46278786659241</v>
+        <v>3.46278810501099</v>
       </c>
       <c r="H51" t="n">
         <v>17000</v>
@@ -1877,7 +1877,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H52" t="n">
         <v>28000</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H53" t="n">
         <v>22000</v>
@@ -1935,7 +1935,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>3.44297242164612</v>
+        <v>3.44297218322754</v>
       </c>
       <c r="H56" t="n">
         <v>4000</v>
@@ -2167,7 +2167,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G62" t="n">
-        <v>3.27453923225403</v>
+        <v>3.27453947067261</v>
       </c>
       <c r="H62" t="n">
         <v>24000</v>
@@ -2312,7 +2312,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H67" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H69" t="n">
         <v>140000</v>
@@ -2428,7 +2428,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G71" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H71" t="n">
         <v>99000</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H72" t="n">
         <v>60000</v>
@@ -2486,7 +2486,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G73" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H73" t="n">
         <v>83000</v>
@@ -2515,7 +2515,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H74" t="n">
         <v>41000</v>
@@ -2573,7 +2573,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G76" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H76" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H80" t="n">
         <v>6000</v>
@@ -2747,7 +2747,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H82" t="n">
         <v>20000</v>
@@ -2776,7 +2776,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G83" t="n">
-        <v>3.30426287651062</v>
+        <v>3.30426263809204</v>
       </c>
       <c r="H83" t="n">
         <v>8000</v>
@@ -2863,7 +2863,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G86" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H86" t="n">
         <v>32000</v>
@@ -2892,7 +2892,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G87" t="n">
-        <v>3.43306446075439</v>
+        <v>3.43306469917297</v>
       </c>
       <c r="H87" t="n">
         <v>34000</v>
@@ -2950,7 +2950,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G89" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -2979,7 +2979,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G90" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H90" t="n">
         <v>11000</v>
@@ -3008,7 +3008,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>3.35380172729492</v>
+        <v>3.3538019657135</v>
       </c>
       <c r="H91" t="n">
         <v>14000</v>
@@ -3066,7 +3066,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G93" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H93" t="n">
         <v>2000</v>
@@ -3095,7 +3095,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H94" t="n">
         <v>3000</v>
@@ -3124,7 +3124,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H95" t="n">
         <v>10000</v>
@@ -3182,7 +3182,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H97" t="n">
         <v>62000</v>
@@ -3211,7 +3211,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H98" t="n">
         <v>12000</v>
@@ -3240,7 +3240,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>3.16555285453796</v>
+        <v>3.16555309295654</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H100" t="n">
         <v>48000</v>
@@ -3298,7 +3298,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H101" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G102" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H102" t="n">
         <v>52000</v>
@@ -3414,7 +3414,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G105" t="n">
-        <v>3.37361741065979</v>
+        <v>3.37361764907837</v>
       </c>
       <c r="H105" t="n">
         <v>23000</v>
@@ -3472,7 +3472,7 @@
         <v>3.25</v>
       </c>
       <c r="G107" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H107" t="n">
         <v>13000</v>
@@ -3501,7 +3501,7 @@
         <v>3.25</v>
       </c>
       <c r="G108" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H108" t="n">
         <v>26000</v>
@@ -3849,7 +3849,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H120" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H121" t="n">
         <v>11000</v>
@@ -3907,7 +3907,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H122" t="n">
         <v>12000</v>
@@ -4052,7 +4052,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H127" t="n">
         <v>6000</v>
@@ -4197,7 +4197,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G132" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H132" t="n">
         <v>5000</v>
@@ -4226,7 +4226,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G133" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G134" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H134" t="n">
         <v>191000</v>
@@ -4284,7 +4284,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>3.63122129440308</v>
+        <v>3.6312210559845</v>
       </c>
       <c r="H135" t="n">
         <v>74000</v>
@@ -4400,7 +4400,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.76002311706543</v>
+        <v>3.76002335548401</v>
       </c>
       <c r="H139" t="n">
         <v>8000</v>
@@ -4429,7 +4429,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G140" t="n">
-        <v>3.68571448326111</v>
+        <v>3.68571424484253</v>
       </c>
       <c r="H140" t="n">
         <v>21000</v>
@@ -4487,7 +4487,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4545,7 +4545,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G144" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4719,7 +4719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G150" t="n">
-        <v>3.61635947227478</v>
+        <v>3.61635971069336</v>
       </c>
       <c r="H150" t="n">
         <v>4000</v>
@@ -4864,7 +4864,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G155" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H155" t="n">
         <v>10000</v>
@@ -4893,7 +4893,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G156" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H156" t="n">
         <v>19000</v>
@@ -4951,7 +4951,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G158" t="n">
-        <v>3.6411292552948</v>
+        <v>3.64112901687622</v>
       </c>
       <c r="H158" t="n">
         <v>5000</v>
@@ -4980,7 +4980,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G159" t="n">
-        <v>3.60645198822021</v>
+        <v>3.60645174980164</v>
       </c>
       <c r="H159" t="n">
         <v>14000</v>
@@ -5038,7 +5038,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G161" t="n">
-        <v>3.56186628341675</v>
+        <v>3.56186652183533</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5125,7 +5125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G164" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H164" t="n">
         <v>72000</v>
@@ -5154,7 +5154,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H165" t="n">
         <v>24000</v>
@@ -5183,7 +5183,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G166" t="n">
-        <v>2.98225831985474</v>
+        <v>2.98225808143616</v>
       </c>
       <c r="H166" t="n">
         <v>26000</v>
@@ -5357,7 +5357,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.66520762443542</v>
+        <v>2.66520738601685</v>
       </c>
       <c r="H172" t="n">
         <v>17000</v>
@@ -5560,7 +5560,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G179" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H179" t="n">
         <v>25000</v>
@@ -5618,7 +5618,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G181" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H181" t="n">
         <v>64000</v>
@@ -5676,7 +5676,7 @@
         <v>3.25</v>
       </c>
       <c r="G183" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>3.25</v>
       </c>
       <c r="G184" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G185" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H186" t="n">
         <v>7000</v>
@@ -5821,7 +5821,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G188" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H188" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H190" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G195" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H195" t="n">
         <v>2000</v>
@@ -6053,7 +6053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G196" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H204" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G210" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H210" t="n">
         <v>29000</v>
@@ -6488,7 +6488,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.25</v>
       </c>
       <c r="G212" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H212" t="n">
         <v>15000</v>
@@ -6546,7 +6546,7 @@
         <v>3.25</v>
       </c>
       <c r="G213" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H213" t="n">
         <v>22000</v>
@@ -6575,7 +6575,7 @@
         <v>3.25</v>
       </c>
       <c r="G214" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H214" t="n">
         <v>4000</v>
@@ -6604,7 +6604,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H215" t="n">
         <v>28000</v>
@@ -6633,7 +6633,7 @@
         <v>3.25</v>
       </c>
       <c r="G216" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H216" t="n">
         <v>12000</v>
@@ -6691,7 +6691,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G218" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H219" t="n">
         <v>11000</v>
@@ -6749,7 +6749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G220" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H220" t="n">
         <v>16000</v>
@@ -6778,7 +6778,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G221" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H221" t="n">
         <v>30000</v>
@@ -6807,7 +6807,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G222" t="n">
-        <v>3.39838743209839</v>
+        <v>3.39838719367981</v>
       </c>
       <c r="H222" t="n">
         <v>13000</v>
@@ -6865,7 +6865,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H224" t="n">
         <v>11000</v>
@@ -6923,7 +6923,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G226" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H226" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H229" t="n">
         <v>4000</v>
@@ -7039,7 +7039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>3.25</v>
       </c>
       <c r="G231" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H231" t="n">
         <v>7000</v>
@@ -7097,7 +7097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H232" t="n">
         <v>8000</v>
@@ -7184,7 +7184,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H235" t="n">
         <v>5000</v>
@@ -7213,7 +7213,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>3.54700469970703</v>
+        <v>3.54700446128845</v>
       </c>
       <c r="H236" t="n">
         <v>52000</v>
@@ -7242,7 +7242,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G241" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H241" t="n">
         <v>2000</v>
@@ -7474,7 +7474,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H245" t="n">
         <v>2000</v>
@@ -7590,7 +7590,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7648,7 +7648,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H251" t="n">
         <v>1000</v>
@@ -8054,7 +8054,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8083,7 +8083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G271" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H273" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G274" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G275" t="n">
-        <v>3.28940105438232</v>
+        <v>3.28940081596375</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G278" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G279" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G289" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H289" t="n">
         <v>3000</v>
@@ -8779,7 +8779,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G291" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H291" t="n">
         <v>9000</v>
@@ -8837,7 +8837,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G293" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H293" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G296" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H296" t="n">
         <v>2000</v>
@@ -9069,7 +9069,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G300" t="n">
-        <v>3.11105990409851</v>
+        <v>3.11106014251709</v>
       </c>
       <c r="H300" t="n">
         <v>5000</v>
@@ -9098,7 +9098,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G301" t="n">
-        <v>3.13087558746338</v>
+        <v>3.13087582588196</v>
       </c>
       <c r="H301" t="n">
         <v>10000</v>
@@ -9301,7 +9301,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H317" t="n">
         <v>4000</v>
@@ -9591,7 +9591,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G319" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H319" t="n">
         <v>3000</v>
@@ -9649,7 +9649,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H320" t="n">
         <v>4000</v>
@@ -9678,7 +9678,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H321" t="n">
         <v>5000</v>
@@ -9736,7 +9736,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H323" t="n">
         <v>2000</v>
@@ -9765,7 +9765,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G324" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G326" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H326" t="n">
         <v>1000</v>
@@ -9852,7 +9852,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G328" t="n">
-        <v>2.87327218055725</v>
+        <v>2.87327194213867</v>
       </c>
       <c r="H328" t="n">
         <v>3000</v>
@@ -9939,7 +9939,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G330" t="n">
-        <v>2.95253467559814</v>
+        <v>2.95253443717957</v>
       </c>
       <c r="H330" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H342" t="n">
         <v>1000</v>
@@ -10403,7 +10403,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>3.1407835483551</v>
+        <v>3.14078378677368</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>3.25</v>
       </c>
       <c r="G350" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H350" t="n">
         <v>5000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H351" t="n">
         <v>10000</v>
@@ -10577,7 +10577,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G352" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H352" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G353" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H353" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G354" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H355" t="n">
         <v>3000</v>
@@ -10693,7 +10693,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G357" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H357" t="n">
         <v>2000</v>
@@ -10751,7 +10751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G358" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H358" t="n">
         <v>1000</v>
@@ -10780,7 +10780,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G359" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H359" t="n">
         <v>61000</v>
@@ -10809,7 +10809,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G360" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G363" t="n">
-        <v>3.43801856040955</v>
+        <v>3.43801832199097</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H366" t="n">
         <v>1000</v>
@@ -11012,7 +11012,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G375" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H375" t="n">
         <v>3000</v>
@@ -11273,7 +11273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.38847947120667</v>
+        <v>3.38847923278809</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G378" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H378" t="n">
         <v>4000</v>
@@ -11360,7 +11360,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G379" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H380" t="n">
         <v>1000</v>
@@ -11418,7 +11418,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G385" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H385" t="n">
         <v>38000</v>
@@ -11563,7 +11563,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G386" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G387" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G388" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H388" t="n">
         <v>40000</v>
@@ -11650,7 +11650,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G389" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G391" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H391" t="n">
         <v>6000</v>
@@ -11766,7 +11766,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H393" t="n">
         <v>2000</v>
@@ -11795,7 +11795,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G394" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G395" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H395" t="n">
         <v>1000</v>
@@ -11853,7 +11853,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G396" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G401" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H401" t="n">
         <v>1000</v>
@@ -12201,7 +12201,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G408" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.23986172676086</v>
+        <v>3.23986196517944</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>3.25</v>
       </c>
       <c r="G410" t="n">
-        <v>3.220046043396</v>
+        <v>3.22004628181458</v>
       </c>
       <c r="H410" t="n">
         <v>7000</v>
@@ -12288,7 +12288,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H411" t="n">
         <v>3000</v>
@@ -12317,7 +12317,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G413" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20023059844971</v>
+        <v>3.20023036003113</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H416" t="n">
         <v>1000</v>
@@ -12462,7 +12462,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G417" t="n">
-        <v>3.17050719261169</v>
+        <v>3.17050695419312</v>
       </c>
       <c r="H417" t="n">
         <v>3000</v>
@@ -12665,7 +12665,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>3.31912422180176</v>
+        <v>3.31912446022034</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12752,7 +12752,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G427" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H427" t="n">
         <v>3000</v>
@@ -12984,7 +12984,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G435" t="n">
-        <v>3.35875606536865</v>
+        <v>3.35875582695007</v>
       </c>
       <c r="H435" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>3.50737309455872</v>
+        <v>3.50737333297729</v>
       </c>
       <c r="H440" t="n">
         <v>5000</v>
@@ -13158,7 +13158,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G441" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H441" t="n">
         <v>1000</v>
@@ -13187,7 +13187,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.51728105545044</v>
+        <v>3.51728129386902</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>3.58663606643677</v>
+        <v>3.58663582801819</v>
       </c>
       <c r="H443" t="n">
         <v>9000</v>
@@ -13419,7 +13419,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H450" t="n">
         <v>23000</v>
@@ -13448,7 +13448,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G451" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>3.52718877792358</v>
+        <v>3.52718901634216</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H453" t="n">
         <v>2000</v>
@@ -13535,7 +13535,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G454" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H459" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>3.42811059951782</v>
+        <v>3.4281108379364</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G461" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H461" t="n">
         <v>1000</v>
@@ -13767,7 +13767,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G462" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G463" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G465" t="n">
-        <v>3.40829491615295</v>
+        <v>3.40829515457153</v>
       </c>
       <c r="H465" t="n">
         <v>1000</v>
@@ -13883,7 +13883,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G466" t="n">
-        <v>3.32903218269348</v>
+        <v>3.32903242111206</v>
       </c>
       <c r="H466" t="n">
         <v>1000</v>
@@ -14086,7 +14086,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G473" t="n">
-        <v>3.24976968765259</v>
+        <v>3.24976944923401</v>
       </c>
       <c r="H473" t="n">
         <v>5000</v>
@@ -39568,7 +39568,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="D1352" t="n">
-        <v>3.09999990463257</v>
+        <v>3.14000010490417</v>
       </c>
       <c r="E1352" t="n">
         <v>3.03999996185303</v>
@@ -39580,9 +39580,38 @@
         <v>3.14000010490417</v>
       </c>
       <c r="H1352" t="n">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="I1352" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1353" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="H1353" t="n">
+        <v>29000</v>
+      </c>
+      <c r="I1353" t="s">
         <v>9</v>
       </c>
     </row>
